--- a/Bulk_Device_Import_Template.xlsx
+++ b/Bulk_Device_Import_Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\shared\openDCIM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\open-dcim\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36B4B8D-4A8F-442E-9186-DC51D3774679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="90" windowWidth="20115" windowHeight="12585"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,12 +78,6 @@
     <t>CustomTags</t>
   </si>
   <si>
-    <t>OSTI</t>
-  </si>
-  <si>
-    <t>OSTI.AO14</t>
-  </si>
-  <si>
     <t>Test-Server01</t>
   </si>
   <si>
@@ -92,13 +87,19 @@
     <t>Proliant DL 360 G7</t>
   </si>
   <si>
-    <t>CCSD</t>
+    <t>RST#2nd</t>
+  </si>
+  <si>
+    <t>CB01</t>
+  </si>
+  <si>
+    <t>CNO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -149,9 +150,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,9 +190,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -226,7 +227,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -261,7 +262,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -434,26 +435,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="6" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="12" width="10.5703125" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
-    <col min="16" max="16" width="22.28515625" customWidth="1"/>
-    <col min="17" max="17" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" customWidth="1"/>
+    <col min="6" max="7" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" customWidth="1"/>
+    <col min="9" max="9" width="13.7265625" customWidth="1"/>
+    <col min="10" max="12" width="10.54296875" customWidth="1"/>
+    <col min="13" max="13" width="7.54296875" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" customWidth="1"/>
+    <col min="16" max="16" width="22.26953125" customWidth="1"/>
+    <col min="17" max="17" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,27 +510,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <v>1234</v>
@@ -539,46 +540,46 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N16" s="1"/>
     </row>
   </sheetData>
@@ -587,18 +588,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
